--- a/stats/di_expert_v1.xlsx
+++ b/stats/di_expert_v1.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D8"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -421,77 +421,105 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>EXTREME_BUY</v>
+        <v>STRONG_BUY</v>
       </c>
       <c r="B2">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="C2">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>-5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>BUY</v>
+        <v>SOLID_BUY</v>
       </c>
       <c r="B3">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>BALANCED</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v>±5</v>
+        <v>WEAK_BUY</v>
+      </c>
+      <c r="B4">
+        <v>-5</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SELL</v>
+        <v>BALANCED</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="C5">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>-8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>EXTREME_SELL</v>
+        <v>WEAK_SELL</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SOLID_SELL</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>-8</v>
+      </c>
+      <c r="D7">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>STRONG_SELL</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>-5</v>
+      </c>
+      <c r="D8">
+        <v>-8</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
   </ignoredErrors>
 </worksheet>
 </file>